--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEVADA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEVADA_2021.xlsx
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C166">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C276">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C285">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C793">
@@ -15180,7 +15180,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C824">
